--- a/public/data/builtin/xlsx/korea_sido_grdp.xlsx
+++ b/public/data/builtin/xlsx/korea_sido_grdp.xlsx
@@ -574,7 +574,7 @@
         <v>강원특별자치도</v>
       </c>
       <c r="B11" t="str">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C11">
         <v>47.3</v>
@@ -625,7 +625,7 @@
         <v>전북특별자치도</v>
       </c>
       <c r="B14" t="str">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C14">
         <v>50.2</v>
